--- a/data/cambridge_event_sources_v0.7.xlsx
+++ b/data/cambridge_event_sources_v0.7.xlsx
@@ -2512,27 +2512,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S019</t>
+          <t>S029</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cambridge City FC</t>
+          <t>Let's Do This — Cambridgeshire</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.cambridgecityfc.com/fixtures/</t>
+          <t>https://www.letsdothis.com/gb/running-events-in-cambridgeshire</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>страница отвечает ошибкой</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 200; страница: 404</t>
+          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2540,10 +2540,14 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>забеги и триатлоны с регистрацией</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>перепроверить позже</t>
+          <t>проверить вручную</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2560,27 +2564,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S020</t>
+          <t>S036</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cambridge Rugby Club</t>
+          <t>Cambridge Literary Festival</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.cambridgerugbyclub.co.uk/fixtures</t>
+          <t>https://www.cambridgeliteraryfestival.com/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>обрыв соединения</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP -1</t>
+          <t>robots.txt: HTTP 200; страница: 403</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2590,12 +2594,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>домашние матчи Cambridge RUFC</t>
+          <t>Cambridge Literary Festival (весна, осень)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>перепроверить позже</t>
+          <t>проверить вручную</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2612,17 +2616,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S029</t>
+          <t>S041</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Let's Do This — Cambridgeshire</t>
+          <t>Cambridge Arts Theatre</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.letsdothis.com/gb/running-events-in-cambridgeshire</t>
+          <t>https://www.cambridgeartstheatre.com/whats-on</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2632,7 +2636,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
+          <t>robots.txt: HTTP 200; страница: 403</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2642,7 +2646,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>забеги и триатлоны с регистрацией</t>
+          <t>афиша Arts Theatre (есть через Ents24)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2664,17 +2668,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S036</t>
+          <t>S053</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cambridge Literary Festival</t>
+          <t>IWM Duxford</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.cambridgeliteraryfestival.com/</t>
+          <t>https://www.iwm.org.uk/events/iwm-duxford</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2694,7 +2698,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cambridge Literary Festival (весна, осень)</t>
+          <t>авиашоу и события IWM Duxford</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2716,17 +2720,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S041</t>
+          <t>S063</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cambridge Arts Theatre</t>
+          <t>Resident Advisor / Skiddle — клубные события</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.cambridgeartstheatre.com/whats-on</t>
+          <t>https://ra.co/events/uk/cambridge</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2744,11 +2748,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>афиша Arts Theatre (есть через Ents24)</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -2768,27 +2768,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S053</t>
+          <t>S088</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IWM Duxford</t>
+          <t>parkrun — Cambridge, Wimpole и др.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.iwm.org.uk/events/iwm-duxford</t>
+          <t>https://www.parkrun.org.uk/cambridge/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница отвечает 403</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 200; страница: 403</t>
+          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>авиашоу и события IWM Duxford</t>
+          <t>спецзабеги parkrun (Рождество, Новый год)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2820,27 +2820,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S063</t>
+          <t>S089</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Resident Advisor / Skiddle — клубные события</t>
+          <t>Town and Gown 10k</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://ra.co/events/uk/cambridge</t>
+          <t>https://www.townandgown10k.com/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница отвечает 403</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 200; страница: 403</t>
+          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2848,7 +2848,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>дата Town &amp; Gown 10K (найдена поиском)</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -2868,17 +2872,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S088</t>
+          <t>S100</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>parkrun — Cambridge, Wimpole и др.</t>
+          <t>Huntingdonshire District Council</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.parkrun.org.uk/cambridge/</t>
+          <t>https://www.ticketsource.co.uk/hinchingbrooke-country-park</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2898,7 +2902,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>спецзабеги parkrun (Рождество, Новый год)</t>
+          <t>события Hinchingbrooke Country Park (TicketSource)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2920,22 +2924,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S089</t>
+          <t>S101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Town and Gown 10k</t>
+          <t>Fenland District Council</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.townandgown10k.com/</t>
+          <t>https://www.fenland.gov.uk/events</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>страница отвечает 403</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2948,11 +2952,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>дата Town &amp; Gown 10K (найдена поиском)</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -2972,22 +2972,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>S103</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huntingdonshire District Council</t>
+          <t>Ely City Council</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.ticketsource.co.uk/hinchingbrooke-country-park</t>
+          <t>https://www.cityofelycouncil.org.uk/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>страница отвечает 403</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3000,11 +3000,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>события Hinchingbrooke Country Park (TicketSource)</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -3024,17 +3020,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>S104</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fenland District Council</t>
+          <t>St Ives Town Council</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.fenland.gov.uk/events</t>
+          <t>https://www.stivestowncouncil.gov.uk/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3072,17 +3068,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S103</t>
+          <t>S106</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ely City Council</t>
+          <t>Huntingdon Town Council</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.cityofelycouncil.org.uk/</t>
+          <t>https://www.huntingdontown.gov.uk/council_events/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3120,17 +3116,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S104</t>
+          <t>S112</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>St Ives Town Council</t>
+          <t>Soham Town Council</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.stivestowncouncil.gov.uk/</t>
+          <t>https://www.soham-tc.gov.uk/council_events/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3168,17 +3164,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S106</t>
+          <t>S114</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Huntingdon Town Council</t>
+          <t>Visit Peterborough</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.huntingdontown.gov.uk/council_events/</t>
+          <t>https://www.visitpeterborough.com/whats-on</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3196,7 +3192,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>события Питерборо из Visit Peterborough</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -3216,27 +3216,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S112</t>
+          <t>S120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Soham Town Council</t>
+          <t>Peterborough Cathedral</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.soham-tc.gov.uk/council_events/</t>
+          <t>https://peterborough-cathedral.org.uk/whats-on/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница отвечает ошибкой</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
+          <t>robots.txt: HTTP 200; страница: 404</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3244,10 +3244,14 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>концерты собора Питерборо (часть — Ents24/Skiddle)</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>проверить вручную</t>
+          <t>перепроверить позже</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3264,17 +3268,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S114</t>
+          <t>S127</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visit Peterborough</t>
+          <t>Saffron Walden / Newmarket — Town Councils</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.visitpeterborough.com/whats-on</t>
+          <t>https://www.saffronwalden.gov.uk/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3284,7 +3288,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
+          <t>robots.txt: HTTP 200; страница: 403</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3292,11 +3296,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>события Питерборо из Visit Peterborough</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -3316,27 +3316,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S120</t>
+          <t>S133</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peterborough Cathedral</t>
+          <t>Nene Park / Ferry Meadows</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://peterborough-cathedral.org.uk/whats-on/</t>
+          <t>https://www.nenepark.org.uk/events/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>страница отвечает ошибкой</t>
+          <t>обрыв соединения</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 200; страница: 404</t>
+          <t>robots.txt: HTTP -1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>концерты собора Питерборо (часть — Ents24/Skiddle)</t>
+          <t>события Ferry Meadows / Nene Park</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3368,27 +3368,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S127</t>
+          <t>S135</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Saffron Walden / Newmarket — Town Councils</t>
+          <t>Shepreth Wildlife Park</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.saffronwalden.gov.uk/</t>
+          <t>https://www.sheprethwildlifepark.co.uk/</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница отвечает 403</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 200; страница: 403</t>
+          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3396,7 +3396,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>события Shepreth Wildlife Park</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>проверить вручную</t>
@@ -3416,27 +3420,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S133</t>
+          <t>S142</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nene Park / Ferry Meadows</t>
+          <t>ChurchSuite</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.nenepark.org.uk/events/</t>
+          <t>https://churchsuite.com/</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>обрыв соединения</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP -1</t>
+          <t>robots.txt: HTTP 200; страница: 403</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3446,12 +3450,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>события Ferry Meadows / Nene Park</t>
+          <t>календари приходов на ChurchSuite</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>перепроверить позже</t>
+          <t>проверить вручную</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3468,27 +3472,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S135</t>
+          <t>S156</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shepreth Wildlife Park</t>
+          <t>Vue Cambridge (The Grafton)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.sheprethwildlifepark.co.uk/</t>
+          <t>https://www.myvue.com/cinema/cambridge/whats-on</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>страница отвечает 403</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 403 (4xx — правил нет, RFC 9309); страница: 403</t>
+          <t>robots.txt 200; страница 403 (бот-защита)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3498,12 +3502,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>события Shepreth Wildlife Park</t>
+          <t>новые фильмы и спецпоказы Vue</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>проверить вручную</t>
+          <t>перепроверить позже; найти поиском</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3520,27 +3524,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S142</t>
+          <t>S157</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ChurchSuite</t>
+          <t>Light Cinema Cambridge (Leisure Park)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://churchsuite.com/</t>
+          <t>https://www.thelight.co.uk/cinema/cambridge</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница только на скриптах</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>robots.txt: HTTP 200; страница: 403</t>
+          <t>страница без текста — афиша только скриптом</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3550,12 +3554,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>календари приходов на ChurchSuite</t>
+          <t>новые фильмы и спецпоказы Light</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>проверить вручную</t>
+          <t>перепроверить позже; найти поиском</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3572,17 +3576,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S156</t>
+          <t>S158</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vue Cambridge (The Grafton)</t>
+          <t>Saffron Screen (Saffron Walden)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.myvue.com/cinema/cambridge/whats-on</t>
+          <t>https://www.saffronscreen.com/</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>robots.txt 200; страница 403 (бот-защита)</t>
+          <t>HTTP 202, заглушка бот-защиты</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3602,7 +3606,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>новые фильмы и спецпоказы Vue</t>
+          <t>фильмы и спецпоказы Saffron Screen</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3624,27 +3628,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S157</t>
+          <t>S159</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Light Cinema Cambridge (Leisure Park)</t>
+          <t>Babylon Cinema (Ely Maltings)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.thelight.co.uk/cinema/cambridge</t>
+          <t>https://www.babylonely.co.uk/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>страница только на скриптах</t>
+          <t>обрыв соединения</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>страница без текста — афиша только скриптом</t>
+          <t>robots.txt: обрыв соединения</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3654,7 +3658,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>новые фильмы и спецпоказы Light</t>
+          <t>фильмы Babylon Ely</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3676,17 +3680,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S158</t>
+          <t>S160</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Saffron Screen (Saffron Walden)</t>
+          <t>CURUFC — Cambridge University Rugby (Grange Road)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.saffronscreen.com/</t>
+          <t>https://curufc.com/events-tickets/fixtures/</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3706,7 +3710,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>фильмы и спецпоказы Saffron Screen</t>
+          <t>матчи университетского регби с публикой</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3728,27 +3732,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S159</t>
+          <t>S161</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Babylon Cinema (Ely Maltings)</t>
+          <t>FA Full-Time (нелиговый и женский футбол)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.babylonely.co.uk/</t>
+          <t>https://fulltime.thefa.com/</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>обрыв соединения</t>
+          <t>заглушка или проверка бот-защиты</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>robots.txt: обрыв соединения</t>
+          <t>robots.txt 403 (правил нет), страница 403</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3758,7 +3762,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>фильмы Babylon Ely</t>
+          <t>календари нелиговых и женских команд</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3780,17 +3784,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S160</t>
+          <t>S162</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CURUFC — Cambridge University Rugby (Grange Road)</t>
+          <t>Cambridge Kids Club</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://curufc.com/events-tickets/fixtures/</t>
+          <t>https://cambridgekidsclub.com/holiday-playschemes/</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3800,7 +3804,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HTTP 202, заглушка бот-защиты</t>
+          <t>Cloudflare challenge (cf-mitigated: challenge)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3810,12 +3814,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>матчи университетского регби с публикой</t>
+          <t>playscheme на октябрьские каникулы: 9 площадок, 4–11 лет</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>перепроверить позже; найти поиском</t>
+          <t>проверить вручную; запросить у организатора</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3832,27 +3836,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S161</t>
+          <t>P:childcare.admin.cam.ac.uk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FA Full-Time (нелиговый и женский футбол)</t>
+          <t>University of Cambridge Childcare Office — University Holiday Playscheme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://fulltime.thefa.com/</t>
+          <t>https://www.childcare.admin.cam.ac.uk/university-holiday-playscheme</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница отвечает 403</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>robots.txt 403 (правил нет), страница 403</t>
+          <t>страница провайдера открылась</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3862,12 +3866,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>календари нелиговых и женских команд</t>
+          <t>каникулярные программы провайдера</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>перепроверить позже; найти поиском</t>
+          <t>проверить вручную; найти поиском</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3877,34 +3881,34 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>открыто</t>
+          <t>решено</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S162</t>
+          <t>P:nenepark.org.uk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cambridge Kids Club</t>
+          <t>Nene Park</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://cambridgekidsclub.com/holiday-playschemes/</t>
+          <t>https://nenepark.org.uk/holiday-club</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>заглушка или проверка бот-защиты</t>
+          <t>страница отвечает 403</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cloudflare challenge (cf-mitigated: challenge)</t>
+          <t>страница провайдера открылась</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3914,12 +3918,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>playscheme на октябрьские каникулы: 9 площадок, 4–11 лет</t>
+          <t>каникулярные программы провайдера</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>проверить вручную; запросить у организатора</t>
+          <t>проверить вручную; найти поиском</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3929,24 +3933,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>открыто</t>
+          <t>решено</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P:childcare.admin.cam.ac.uk</t>
+          <t>P:sport.cam.ac.uk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of Cambridge Childcare Office — University Holiday Playscheme</t>
+          <t>Sport at Cambridge — children's athletics camps</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.childcare.admin.cam.ac.uk/university-holiday-playscheme</t>
+          <t>https://www.sport.cam.ac.uk/childrens-athletic-camps</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3988,27 +3992,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P:nenepark.org.uk</t>
+          <t>S019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nene Park</t>
+          <t>Cambridge City FC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://nenepark.org.uk/holiday-club</t>
+          <t>https://www.cambridgecityfc.com/fixtures/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>страница отвечает 403</t>
+          <t>страница отвечает ошибкой</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>страница провайдера открылась</t>
+          <t>подключён: события на главной cambridgecityfc.com (страница /fixtures/ — 404)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4016,14 +4020,10 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>каникулярные программы провайдера</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>проверить вручную; найти поиском</t>
+          <t>перепроверить позже</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4040,27 +4040,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P:sport.cam.ac.uk</t>
+          <t>S020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sport at Cambridge — children's athletics camps</t>
+          <t>Cambridge Rugby Club</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.sport.cam.ac.uk/childrens-athletic-camps</t>
+          <t>https://www.cambridgerugbyclub.co.uk/fixtures</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>страница отвечает 403</t>
+          <t>обрыв соединения</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>страница провайдера открылась</t>
+          <t>подключён: календарь National League 1 — PDF на nationalleaguerugby.com (сайт клуба закрыт)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>каникулярные программы провайдера</t>
+          <t>домашние матчи Cambridge RUFC</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>проверить вручную; найти поиском</t>
+          <t>перепроверить позже</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
